--- a/scrubbing_process/Batch # 1 - $119,802.46.xlsx
+++ b/scrubbing_process/Batch # 1 - $119,802.46.xlsx
@@ -28343,7 +28343,11 @@
           <t>DELTA AIR LINES</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>1035</t>
@@ -28404,7 +28408,11 @@
           <t>AMERICAN AIRLINES</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>American</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>4263</t>
@@ -28465,7 +28473,11 @@
           <t>MILOS, INC.</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Milos</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>6470</t>
@@ -28526,7 +28538,11 @@
           <t>United</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>United</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>6645</t>
@@ -28587,7 +28603,11 @@
           <t>UNITED AIRLINES ARC</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>United</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>1035</t>
@@ -28648,7 +28668,11 @@
           <t>DELTA AIR LINES</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>1035</t>
@@ -28709,7 +28733,11 @@
           <t>TRAVEL AGENCY SERVICES</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Frosch</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>6645</t>
@@ -28770,7 +28798,11 @@
           <t>THE UMSTEAD HTL &amp; SPA</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Umstead</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>4263</t>
@@ -28831,7 +28863,11 @@
           <t>THE UMSTEAD HTL &amp; SPA</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Umstead</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>6409</t>
@@ -28892,7 +28928,11 @@
           <t>THE UMSTEAD HTL &amp; SPA</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Umstead</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>6409</t>
@@ -28953,7 +28993,11 @@
           <t>THE UMSTEAD HTL &amp; SPA</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Umstead</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>6409</t>
@@ -29014,7 +29058,11 @@
           <t>THE UMSTEAD HTL &amp; SPA</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Umstead</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>4263</t>
@@ -29075,7 +29123,11 @@
           <t>SUMMIT EXPRESS NJ</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Summit Express</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>6454</t>
@@ -29136,7 +29188,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>1035</t>
@@ -29197,7 +29253,11 @@
           <t>501 ON MAIN</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>501 On Main</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>1035</t>
@@ -29258,7 +29318,11 @@
           <t>SUMMIT EXPRESS NJ</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Summit Express</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>6961</t>
@@ -29319,7 +29383,11 @@
           <t>SUMMIT EXPRESS NJ</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Summit Express</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>6456</t>
@@ -29380,7 +29448,11 @@
           <t>IL GATTOPARDO</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Il Gattopardo</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>6961</t>
@@ -29443,7 +29515,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>American</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -29506,7 +29578,11 @@
           <t>TRAVEL AGENCY SERVICES</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Frosch</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>1035</t>
@@ -29567,7 +29643,11 @@
           <t>SLC 3054 MAVERIK</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Maverik</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>6001</t>
@@ -29628,7 +29708,11 @@
           <t>DV SILVER LAKE REST</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Silver Lake Restaurant</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>1035</t>
@@ -29689,7 +29773,11 @@
           <t>PROTEIN BAR &amp; KITCHEN</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Protein Bar</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>1035</t>
@@ -29750,7 +29838,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>6448</t>
@@ -29811,7 +29903,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>6448</t>
@@ -29872,7 +29968,11 @@
           <t>Hilton Hotels</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Hilton</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>6448</t>
@@ -29933,7 +30033,11 @@
           <t>DECADENT</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Decadent</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>6448</t>
@@ -29994,7 +30098,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>6448</t>
@@ -30055,7 +30163,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>6448</t>
@@ -30116,7 +30228,11 @@
           <t>PANERA BREAD #ON3788</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Panera Bread</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>6448</t>
@@ -30177,7 +30293,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>6448</t>
@@ -30303,7 +30423,11 @@
           <t>TRAVEL AGENCY SERVICES</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Frosch</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>6915</t>
@@ -30366,7 +30490,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>American</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -30431,7 +30555,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>United</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -30494,7 +30618,11 @@
           <t>TRAVEL AGENCY SERVICES</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Frosch</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>1035</t>
@@ -30555,7 +30683,11 @@
           <t>TRAVEL AGENCY SERVICES</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Frosch</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>6448</t>
@@ -30616,7 +30748,11 @@
           <t>TRAVEL AGENCY SERVICES</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Frosch</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>1008</t>
@@ -30679,7 +30815,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Southwest Airlines</t>
+          <t>Southwest</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -30744,7 +30880,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>United</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -30807,7 +30943,11 @@
           <t>FRANKFURT AIRPORT MARRIOTT HOTEL</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Marriott</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>6915</t>
@@ -30868,7 +31008,11 @@
           <t>FRANKFURT AIRPORT MARRIOTT HOTEL</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Marriott</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>6915</t>
@@ -30929,7 +31073,11 @@
           <t>FONTAINEBLEAU RESORT</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Fontainebleau</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>1001</t>
@@ -30990,7 +31138,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>1001</t>
@@ -31051,7 +31203,11 @@
           <t>SUMMIT ELITE CLASS LIMO</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Summit Elite</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>1001</t>
@@ -31112,7 +31268,11 @@
           <t>SUMMIT ELITE CLASS LIMO</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Summit Elite</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>1001</t>
@@ -31173,7 +31333,11 @@
           <t>UNITED AIRLINES ARC</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>United</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>1035</t>
@@ -31234,7 +31398,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>1001</t>
@@ -31295,7 +31463,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>1001</t>
@@ -31356,7 +31528,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>1001</t>
@@ -31417,7 +31593,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>1001</t>
@@ -31478,7 +31658,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>1001</t>
@@ -31539,7 +31723,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>1001</t>
@@ -31600,7 +31788,11 @@
           <t>DTS NY LUXURY INC</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>DTS NY</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>1008</t>
@@ -31661,7 +31853,11 @@
           <t>NAYA</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Naya</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>4246</t>
@@ -31722,7 +31918,11 @@
           <t>CATER LADY NYC LLC</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Cater Lady</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>4246</t>
@@ -31783,7 +31983,11 @@
           <t>BOINGO WIRELESS, INC.</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Boingo Wireless</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>4001</t>
@@ -31844,7 +32048,11 @@
           <t>STEINERIKSENOSLO</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Stein Eriksen</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>1035</t>
@@ -31905,7 +32113,11 @@
           <t>NOBU 57</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Nobu</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>4001</t>
@@ -31966,7 +32178,11 @@
           <t>DTS NY LUXURY INC</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>DTS NY</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>4263</t>
@@ -32027,7 +32243,11 @@
           <t>DTS NY LUXURY INC</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>DTS NY</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>4001</t>
@@ -32088,7 +32308,11 @@
           <t>DTS NY LUXURY INC</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>DTS NY</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>4001</t>
@@ -32149,7 +32373,11 @@
           <t>DTS NY LUXURY INC</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>DTS NY</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>4001</t>
@@ -32210,7 +32438,11 @@
           <t>DELTA AIR LINES</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>1035</t>
@@ -32271,7 +32503,11 @@
           <t>OMNI BERKSHIRE PLACE CONF</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Omni</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>4246</t>
@@ -32332,7 +32568,11 @@
           <t>DTS NY LUXURY INC</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>DTS NY</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>4001</t>
@@ -32393,7 +32633,11 @@
           <t>GRUBHUB</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Grubhub</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>4001</t>
@@ -32454,7 +32698,11 @@
           <t>DOW JONES &amp; CO INC</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Dow Jones</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>4001</t>
@@ -32515,7 +32763,11 @@
           <t>TRAVEL AGENCY SERVICES</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Frosch</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>1020</t>
@@ -32576,7 +32828,11 @@
           <t>DELTA AIR LINES</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>1020</t>
@@ -32637,7 +32893,11 @@
           <t>ST REGIS DEER VALLEY</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>St. Regis Deer Valley</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>4001</t>
@@ -32698,7 +32958,11 @@
           <t>CARBONE</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Carbone</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>4263</t>
@@ -32759,7 +33023,11 @@
           <t>DTS NY LUXURY INC</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>DTS NY</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>4001</t>
@@ -32820,7 +33088,11 @@
           <t>JETBLUE ARC</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Jetblue</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>4001</t>
@@ -32881,7 +33153,11 @@
           <t>TRAVEL AGENCY SERVICES</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Frosch</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>4001</t>
@@ -32942,7 +33218,11 @@
           <t>DELTA AIR LINES</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>4001</t>
@@ -33003,7 +33283,11 @@
           <t>THE UMSTEAD HTL &amp; SPA</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Umstead</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>4263</t>
@@ -33064,7 +33348,11 @@
           <t>DTS NY LUXURY INC</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>DTS NY</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>4001</t>
@@ -33125,7 +33413,11 @@
           <t>DTS NY LUXURY INC</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>DTS NY</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>1008</t>
@@ -33186,7 +33478,11 @@
           <t>DTS NY LUXURY INC</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>DTS NY</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>4263</t>
@@ -33247,7 +33543,11 @@
           <t>UNITED AIRLINES</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>United</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>4263</t>
@@ -33308,7 +33608,11 @@
           <t>DELTA AIR LINES</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>1035</t>
@@ -33369,7 +33673,11 @@
           <t>ANGUS BARN LTD LLC</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Angus Barn</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>4263</t>
@@ -33430,7 +33738,11 @@
           <t>LA BAIA</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>La Baia</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>4263</t>
@@ -33491,7 +33803,11 @@
           <t>LA BAIA</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>La Baia</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>6470</t>
@@ -33552,7 +33868,11 @@
           <t>THE UMSTEAD HTL &amp; SPA</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Umstead</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>4263</t>
@@ -33613,7 +33933,11 @@
           <t>THE UMSTEAD HTL &amp; SPA</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Umstead</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>4263</t>
@@ -33674,7 +33998,11 @@
           <t>CAFE BOULUD NY</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Cafe Boulud</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>4246</t>
@@ -33735,7 +34063,11 @@
           <t>DELTA AIR LINES</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>2275-M</t>
@@ -33796,7 +34128,11 @@
           <t>DELTA AIR LINES</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>2275-M</t>
@@ -33857,7 +34193,11 @@
           <t>PEI MEDIA INC</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>PEI Media</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>6001</t>
@@ -33918,7 +34258,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>6001</t>
@@ -33981,7 +34325,7 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>American</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -34044,7 +34388,11 @@
           <t>SANTI</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Santi</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>6001</t>
@@ -34105,7 +34453,11 @@
           <t>OMNI BERKSHIRE PLACE</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Omni</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>6001</t>
@@ -34166,7 +34518,11 @@
           <t>OMNI BERKSHIRE PLACE</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Omni</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>6001</t>
@@ -34223,7 +34579,11 @@
           <t>Uber Technologies, Inc</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>1001</t>
@@ -34280,7 +34640,11 @@
           <t>MICROSOFT STORE</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>1008</t>
@@ -34337,7 +34701,11 @@
           <t>Uber Technologies, Inc</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>1001</t>
@@ -34394,7 +34762,11 @@
           <t>Uber Technologies, Inc</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>1001</t>
@@ -34451,7 +34823,11 @@
           <t>LEMA DUMPLING &amp; LE CONGEE T3</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>LeMa Dumpling</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>6450</t>
@@ -34508,7 +34884,11 @@
           <t>GRAB SG - TRANSPORT GL</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Grab Taxi</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>6450</t>
@@ -34565,7 +34945,11 @@
           <t>GRAB SG-TRANSPORT ADY</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Grab Taxi</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>6450</t>
@@ -34622,7 +35006,11 @@
           <t>GRAB SG - TRANSPORT GL</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Grab Taxi</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>6450</t>
@@ -34681,7 +35069,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>Marriott Hotels</t>
+          <t>Marriott</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -34742,7 +35130,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Marriott Hotels</t>
+          <t>Marriott</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -34803,7 +35191,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>Marriott Hotels</t>
+          <t>Marriott</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -34864,7 +35252,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Marriott Hotels</t>
+          <t>Marriott</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -34923,7 +35311,11 @@
           <t>SHANGRI-LA SINGAPORE</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Shangri-La Hotel</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>6450</t>
@@ -34980,7 +35372,11 @@
           <t>SHANGRI-LA SINGAPORE</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Shangri-La Hotel</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>6450</t>
@@ -35039,7 +35435,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>United</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -35100,7 +35496,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>United</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -35159,7 +35555,11 @@
           <t>GZKRSWFWYXGS</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Sheraton</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>6371</t>
@@ -35216,7 +35616,11 @@
           <t>WEI XIN merchant</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Wei Xin</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>6001</t>
@@ -35273,7 +35677,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>1035</t>
@@ -35330,7 +35738,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>1035</t>
@@ -35387,7 +35799,11 @@
           <t>LARK CREEK GRILL</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Lark Creek Grill</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>1035</t>
@@ -35444,7 +35860,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>1035</t>
@@ -35501,7 +35921,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>1035</t>
@@ -35558,7 +35982,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>1035</t>
@@ -35615,7 +36043,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>1035</t>
@@ -35672,7 +36104,11 @@
           <t>SLC THIRST</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Thirst</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>1035</t>
@@ -35729,7 +36165,11 @@
           <t>SLC PANDA EXPRESS</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Panda Express</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>1035</t>
@@ -35786,7 +36226,11 @@
           <t>DELTA AIR LINES</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>1035</t>
@@ -35843,7 +36287,11 @@
           <t>UNITED AIRLINES ARC</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>United</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>1035</t>
@@ -35900,7 +36348,11 @@
           <t>GRUBHUB</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Grubhub</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>1008</t>
@@ -35957,7 +36409,11 @@
           <t>GRUBHUB</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Grubhub</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>1008</t>
@@ -36014,7 +36470,11 @@
           <t>DELTA AIR LINES</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>1035</t>
@@ -36071,7 +36531,11 @@
           <t>TRAVEL AGENCY SERVICES</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Frosch</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>1035</t>
@@ -36128,7 +36592,11 @@
           <t>JETBRAINS AMERICAS INC</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Jetbrains</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>6001</t>
@@ -36185,7 +36653,11 @@
           <t>JETBRAINS AMERICAS INC</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Jetbrains</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>6001</t>
@@ -36242,7 +36714,11 @@
           <t>JETBRAINS AMERICAS INC</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Jetbrains</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>6001</t>
@@ -36303,7 +36779,11 @@
           <t>TRAVEL AGENCY SERVICES</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Frosch</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>6006</t>
@@ -36364,7 +36844,11 @@
           <t>EUROSTAR INTERNATIONAL LTD ARCUS</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Eurostar International</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>6006</t>
@@ -36425,7 +36909,11 @@
           <t>UNITED AIRLINES</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>United</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>6006</t>
@@ -36486,7 +36974,11 @@
           <t>BURGERS AND BOURBON</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Burgers And Bourbon</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>1035</t>
@@ -36547,7 +37039,11 @@
           <t>AUDIBLE, INC.</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Audible</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>1008</t>
@@ -36608,7 +37104,11 @@
           <t>IL MULINO NEW YORK</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Il Mulino</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>1016</t>
@@ -36669,7 +37169,11 @@
           <t>SLC 3044 TRIP ADVISOR</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Trip Advisor</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>1035</t>
@@ -36730,7 +37234,11 @@
           <t>BEANS AND BREWS COFFEE HOUSE S</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Beans &amp; Brews Coffee</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>1035</t>
@@ -36791,7 +37299,11 @@
           <t>CNP MARKET STREET GRILL C</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Market Street Grill</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>1001</t>
@@ -36852,7 +37364,11 @@
           <t>GATERETAIL</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Gateretail</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>1035</t>
@@ -36913,7 +37429,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>1035</t>
@@ -36974,7 +37494,11 @@
           <t>DELTA AIR LINES</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>1035</t>
@@ -37035,7 +37559,11 @@
           <t>DV SILVER LAKE REST</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Silver Lake Restaurant</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>1035</t>
@@ -37096,7 +37624,11 @@
           <t>SLC 3050 SLC ESSENTIALS</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Essen</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>1035</t>
@@ -37157,7 +37689,11 @@
           <t>JFK T5 JACOBS PICKLES 637</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Jacob's Pickles</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>1035</t>
@@ -37218,7 +37754,11 @@
           <t>BURGERS AND BOURBON</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Burgers And Bourbon</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>1035</t>
@@ -37279,7 +37819,11 @@
           <t>ALLIANZ TRAVEL INS</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Allianz</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>1035</t>
@@ -37340,7 +37884,11 @@
           <t>JETBLUE AIRWAYS</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Jetblue</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>1035</t>
@@ -37401,7 +37949,11 @@
           <t>LINKEDIN CORPORATION</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>1001</t>
@@ -37462,7 +38014,11 @@
           <t>CIRCLE K #7510</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Circle K</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>1016</t>
@@ -37523,7 +38079,11 @@
           <t>D.C. CECS PARKING</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>DC Cecs Parking</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>1016</t>
@@ -37584,7 +38144,11 @@
           <t>DUNKIN DONUTS  PC300764</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Dunkin Donuts</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>1016</t>
@@ -37645,7 +38209,11 @@
           <t>HANOVER INN/DRTMTH CLLGE</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Hanover Inn</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>1016</t>
@@ -37706,7 +38274,11 @@
           <t>HANOVER INN/DRTMTH CLLGE</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Hanover Inn</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>1016</t>
@@ -37767,7 +38339,11 @@
           <t>UNITED AIRLINES ARC</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>United</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>1035</t>
@@ -37832,7 +38408,11 @@
           <t>Delta</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>4253</t>
@@ -37893,7 +38473,11 @@
           <t>Delta</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>4253</t>
@@ -37954,7 +38538,11 @@
           <t>JIMMY JOHNS A42 SLC</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Jimmy Johns</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>1035</t>
@@ -38015,7 +38603,11 @@
           <t>TRAVEL AGENCY SERVICES</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Frosch</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>4253</t>
@@ -38076,7 +38668,11 @@
           <t>SPOKANE AIRPORT PARKING</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Spokane Airport Parking</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>1035</t>
@@ -38137,7 +38733,11 @@
           <t>TRAVEL AGENCY SERVICES</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Frosch</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>4253</t>
@@ -38198,7 +38798,11 @@
           <t>DELTA AIR LINES</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>1035</t>
@@ -38259,7 +38863,11 @@
           <t>GEG GREEDY COW BURGER 698</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Geg Greedy Burger</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>1035</t>
@@ -38320,7 +38928,11 @@
           <t>Delta</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>1035</t>
@@ -38381,7 +38993,11 @@
           <t>TRAVEL AGENCY SERVICES</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Frosch</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>1035</t>
@@ -38442,7 +39058,11 @@
           <t>JETBLUE AIRWAYS</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Jetblue</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>1035</t>
@@ -38503,7 +39123,11 @@
           <t>DELTA AIR LINES</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>1035</t>
@@ -38564,7 +39188,11 @@
           <t>JETBLUE AIRWAYS</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Jetblue</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>1035</t>
@@ -38625,7 +39253,11 @@
           <t>HOTEL GIRAFFE</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Hotel Giraffe</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>6454</t>
@@ -38686,7 +39318,11 @@
           <t>HOTEL GIRAFFE</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Hotel Giraffe</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>6454</t>
@@ -38747,7 +39383,11 @@
           <t>HOTEL GIRAFFE</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Hotel Giraffe</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>6454</t>
@@ -38808,7 +39448,11 @@
           <t>THE LXRY COLLECTION HOTL</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>The Luxury Collection Hotel</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>4246</t>
@@ -38869,7 +39513,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>4246</t>
@@ -38930,7 +39578,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>4246</t>
@@ -38991,7 +39643,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>4246</t>
@@ -39052,7 +39708,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>4246</t>
@@ -39113,7 +39773,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>1035</t>
@@ -39174,7 +39838,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>1035</t>
@@ -39235,7 +39903,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>6454</t>
@@ -39296,7 +39968,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>6454</t>
@@ -39357,7 +40033,11 @@
           <t>TRAVEL AGENCY SERVICES</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Frosch</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>1035</t>
@@ -39418,7 +40098,11 @@
           <t>TRAVEL AGENCY SERVICES</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Frosch</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>4246</t>
@@ -39479,7 +40163,11 @@
           <t>TRAVEL AGENCY SERVICES</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Frosch</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>1035</t>
@@ -39540,7 +40228,11 @@
           <t>TRAVEL AGENCY SERVICES</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Frosch</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>4246</t>
@@ -39601,7 +40293,11 @@
           <t>UNITED AIRLINES ARC</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>United</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>4246</t>
@@ -39662,7 +40358,11 @@
           <t>UNITED AIRLINES ARC</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>United</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>1035</t>
@@ -39723,7 +40423,11 @@
           <t>UNITED AIRLINES ARC</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>United</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>4246</t>
@@ -39784,7 +40488,11 @@
           <t>DV SILVER LAKE REST</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Silver Lake Restaurant</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>1035</t>
@@ -39845,7 +40553,11 @@
           <t>YUKI YAMA</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Yuki Yama</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>6001</t>
@@ -39906,7 +40618,11 @@
           <t>SPOTHERO, INC.</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Spothero</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>1008</t>
@@ -39967,7 +40683,11 @@
           <t>UNITED AIRLINES</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>United</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>6001</t>
@@ -40028,7 +40748,11 @@
           <t>AMTRAK AGENCY X</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Amtrak</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>1018-D</t>
@@ -40089,7 +40813,11 @@
           <t>AMTRAK AGENCY X</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Amtrak</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>6454</t>
@@ -40150,7 +40878,11 @@
           <t>AMTRAK.COM</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Amtrak</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>1018-D</t>
@@ -40211,7 +40943,11 @@
           <t>AMTRAK.COM</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Amtrak</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>6454</t>
@@ -40272,7 +41008,11 @@
           <t>TRAVEL AGENCY SERVICES</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Frosch</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>1018-D</t>
@@ -40333,7 +41073,11 @@
           <t>TRAVEL AGENCY SERVICES</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Frosch</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>6454</t>
@@ -40394,7 +41138,11 @@
           <t>DELTA AIR LINES</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>4246</t>
@@ -40455,7 +41203,11 @@
           <t>DELTA AIR LINES</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>1018-D</t>
@@ -40516,7 +41268,11 @@
           <t>TRAVEL AGENCY SERVICES</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Frosch</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>4246</t>
@@ -40577,7 +41333,11 @@
           <t>TRAVEL AGENCY SERVICES</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Frosch</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>1018-D</t>
@@ -40638,7 +41398,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>6001</t>
@@ -40699,7 +41463,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>6001</t>
@@ -40760,7 +41528,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>6001</t>
@@ -40821,7 +41593,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>6001</t>
@@ -40882,7 +41658,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>6001</t>
@@ -40943,7 +41723,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>6001</t>
@@ -41004,7 +41788,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>6001</t>
@@ -41065,7 +41853,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>6001</t>
@@ -41126,7 +41918,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>6001</t>
@@ -41187,7 +41983,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>6001</t>
@@ -41248,7 +42048,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>1035</t>
@@ -41309,7 +42113,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>1035</t>
@@ -41370,7 +42178,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>6001</t>
@@ -41431,7 +42243,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>6001</t>
@@ -41492,7 +42308,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>6001</t>
@@ -41553,7 +42373,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>6001</t>
@@ -41614,7 +42438,11 @@
           <t>PICK UP STIX SLC</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Pick Up Stix</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>1035</t>
@@ -41675,7 +42503,11 @@
           <t>JFK2 SHAKE SHACK B37 1051</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Shake Shack</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>1035</t>
@@ -41736,7 +42568,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>6001</t>
@@ -41797,7 +42633,11 @@
           <t>UNITED AIRLINES</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>United</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>6001</t>
@@ -41858,7 +42698,11 @@
           <t>UNITED AIRLINES</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>United</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>6001</t>
@@ -41919,7 +42763,11 @@
           <t>BNP MEDIA INC</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>BNP Media</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>6487</t>
@@ -41980,7 +42828,11 @@
           <t>UNITED AIRLINES ARC</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>United</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>1016</t>
@@ -42041,7 +42893,11 @@
           <t>TRAVEL AGENCY SERVICES</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Frosch</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>1016</t>
@@ -42102,7 +42958,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>2106</t>
@@ -42163,7 +43023,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>2106</t>
@@ -42224,7 +43088,11 @@
           <t>TATTE BAKERY STORE 630036</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Tatte Bakery</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>2106</t>
@@ -42285,7 +43153,11 @@
           <t>KIMPTON MONACO BALTIMORE</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Kimpton Hotel</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>2106</t>
@@ -42346,7 +43218,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>2106</t>
@@ -42407,7 +43283,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>2106</t>
@@ -42468,7 +43348,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>2106</t>
@@ -42529,7 +43413,11 @@
           <t>UNITED AIRLINES ARC</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>United</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>2106</t>
@@ -42590,7 +43478,11 @@
           <t>TRAVEL AGENCY SERVICES</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Frosch</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>2106</t>
@@ -42651,7 +43543,11 @@
           <t>UNITED AIRLINES ARC</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>United</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>2106</t>
@@ -42712,7 +43608,11 @@
           <t>TRAVEL AGENCY SERVICES</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Frosch</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>2106</t>
@@ -42773,7 +43673,11 @@
           <t>AMTRAK AGENCY X</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Amtrak</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>2106</t>
@@ -42834,7 +43738,11 @@
           <t>TRAVEL AGENCY SERVICES</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Frosch</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>2106</t>
@@ -42895,7 +43803,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>1016</t>
@@ -42956,7 +43868,11 @@
           <t>UNITED AIRLINES</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>United</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>1016</t>
@@ -43017,7 +43933,11 @@
           <t>FAIRMONT GRND  DELMAR</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Grand Del Mar</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>1016</t>
@@ -43078,7 +43998,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>1035</t>
@@ -43139,7 +44063,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>6001</t>
@@ -43200,7 +44128,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>6001</t>
@@ -43261,7 +44193,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>6001</t>
@@ -43322,7 +44258,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>6001</t>
@@ -43383,7 +44323,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>6001</t>
@@ -43444,7 +44388,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>6396</t>
@@ -43505,7 +44453,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>4246</t>
@@ -43566,7 +44518,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>4246</t>
@@ -43627,7 +44583,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>4001</t>
@@ -43688,7 +44648,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>1035</t>
@@ -43749,7 +44713,11 @@
           <t>UBER EATS</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Uber Eats</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>1035</t>
@@ -43810,7 +44778,11 @@
           <t>519 - TRAVEL RIGHT SLC</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Travel Right</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>1035</t>
@@ -43871,7 +44843,11 @@
           <t>UNITED AIRLINES</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>United</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>4001</t>
@@ -43932,7 +44908,11 @@
           <t>SPA MONTAGE</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Spa Montage</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>1035</t>
@@ -43993,7 +44973,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>1035</t>
@@ -44054,7 +45038,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>4001</t>
@@ -44115,7 +45103,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>4001</t>
@@ -44176,7 +45168,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>4001</t>
@@ -44237,7 +45233,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>4001</t>
@@ -44298,7 +45298,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>4001</t>
@@ -44359,7 +45363,11 @@
           <t>BLUE BOTTLE COFFEE</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Blue Bottle</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>4001</t>
@@ -44420,7 +45428,11 @@
           <t>United</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>United</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>1035</t>
@@ -44481,7 +45493,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>4001</t>
@@ -44542,7 +45558,11 @@
           <t>DELTA AIR LINES</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>1035</t>
@@ -44603,7 +45623,11 @@
           <t>TRAVEL AGENCY SERVICES</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Frosch</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>1035</t>
@@ -44664,7 +45688,11 @@
           <t>TRAVEL AGENCY SERVICES</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Frosch</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>1035</t>
@@ -44725,7 +45753,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>4001</t>
@@ -44786,7 +45818,11 @@
           <t>ARABICA MIDTOWN</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Arabica</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>4001</t>
@@ -44847,7 +45883,11 @@
           <t>DOCUSIGN</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Docusign</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>4263</t>
@@ -44908,7 +45948,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>4001</t>
@@ -44969,7 +46013,11 @@
           <t>American Express Initiated Activity</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>1008</t>
@@ -45030,7 +46078,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>4001</t>
@@ -45091,7 +46143,11 @@
           <t>DOCUSIGN</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Docusign</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>4246</t>
@@ -45152,7 +46208,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>4001</t>
@@ -45213,7 +46273,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>4001</t>
@@ -45274,7 +46338,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>4001</t>
@@ -45335,7 +46403,11 @@
           <t>DELTA ONBOARD NON-DISCOUN</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>4001</t>
@@ -45396,7 +46468,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>1035</t>
@@ -45457,7 +46533,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>1035</t>
@@ -45518,7 +46598,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>1035</t>
@@ -45579,7 +46663,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>4001</t>
@@ -45640,7 +46728,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>4001</t>
@@ -45701,7 +46793,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>4001</t>
@@ -45762,7 +46858,11 @@
           <t>AMERICAN AIRLINES</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>American</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>4239</t>
@@ -45823,7 +46923,11 @@
           <t>DELTA AIR LINES</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>4239</t>
@@ -45884,7 +46988,11 @@
           <t>BLUE BOTTLE COFFEE</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Blue Bottle</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>4001</t>
@@ -45945,7 +47053,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>4001</t>
@@ -46006,7 +47118,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>4001</t>
@@ -46067,7 +47183,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>4001</t>
@@ -46128,7 +47248,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>4239</t>
@@ -46189,7 +47313,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>4239</t>
@@ -46250,7 +47378,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>4239</t>
@@ -46311,7 +47443,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>4239</t>
@@ -46372,7 +47508,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>4239</t>
@@ -46433,7 +47573,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>4239</t>
@@ -46494,7 +47638,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>4001</t>
@@ -46555,7 +47703,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>4001</t>
@@ -46616,7 +47768,11 @@
           <t>Delta</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>4239</t>
@@ -46677,7 +47833,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>4001</t>
@@ -46738,7 +47898,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>4001</t>
@@ -46799,7 +47963,11 @@
           <t>TRAVEL AGENCY SERVICES</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Frosch</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>4239</t>
@@ -46860,7 +48028,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>4001</t>
@@ -46921,7 +48093,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>4001</t>
@@ -46982,7 +48158,11 @@
           <t>SANTA MONICA PROPER HOTEL</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Proper Hotel</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>4239</t>
@@ -47043,7 +48223,11 @@
           <t>SANTA MONICA PROPER HOTEL</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Proper Hotel</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>4239</t>
@@ -47104,7 +48288,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>4001</t>
@@ -47165,7 +48353,11 @@
           <t>MEMBERSHIP REWARDS  ADJUSTMENT</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>1008</t>
@@ -47226,7 +48418,11 @@
           <t>MEMBERSHIP REWARDS  ADJUSTMENT</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>1008</t>
@@ -47287,7 +48483,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>4001</t>
@@ -47348,7 +48548,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>4001</t>
@@ -47409,7 +48613,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>4001</t>
@@ -47470,7 +48678,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>4001</t>
@@ -47531,7 +48743,11 @@
           <t>CHIPOTLE 1359</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Chipotle</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>4001</t>
@@ -47592,7 +48808,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>4001</t>
@@ -47653,7 +48873,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>1035</t>
@@ -47714,7 +48938,11 @@
           <t>BURGERS AND BOURBON</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Burgers And Bourbon</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>1035</t>
@@ -47775,7 +49003,11 @@
           <t>BURGERS AND BOURBON</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Burgers And Bourbon</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>1035</t>
@@ -47836,7 +49068,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>1012</t>
@@ -47897,7 +49133,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>1012</t>
@@ -47958,7 +49198,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>1035</t>
@@ -48019,7 +49263,11 @@
           <t>WAL-MART.COM</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>1012</t>
@@ -48080,7 +49328,11 @@
           <t>STATE LIQUOR STORE 37</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>37 Liquor Store</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>1012</t>
@@ -48141,7 +49393,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>4001</t>
@@ -48202,7 +49458,11 @@
           <t>ESTE PIZZA PARK CITY</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Este Pizza</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>1012</t>
@@ -48263,7 +49523,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>4253</t>
@@ -48324,7 +49588,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>4001</t>
@@ -48385,7 +49653,11 @@
           <t>4035 THE MARKETB</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>4035 Market</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>1035</t>
@@ -48446,7 +49718,11 @@
           <t>519 - TRAVEL RIGHT SLC</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Travel Right</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>1035</t>
@@ -48507,7 +49783,11 @@
           <t>BURGERS AND BOURBON</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Burgers And Bourbon</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>1035</t>
@@ -48568,7 +49848,11 @@
           <t>DELTA AIR LINES</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>1035</t>
@@ -48629,7 +49913,11 @@
           <t>DEVOCION - LEXINGTON NEW</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Devocion</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>4001</t>
@@ -48690,7 +49978,11 @@
           <t>JETBLUE AIRWAYS</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Jetblue</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>1035</t>
@@ -48751,7 +50043,11 @@
           <t>JETBLUE ARC</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Jetblue</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>1035</t>
@@ -48812,7 +50108,11 @@
           <t>TRAVEL AGENCY SERVICES</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Frosch</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>1035</t>
@@ -48873,7 +50173,11 @@
           <t>TRAVEL AGENCY SERVICES</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Frosch</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>1035</t>
@@ -48934,7 +50238,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>4001</t>
@@ -48995,7 +50303,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>4001</t>
@@ -49056,7 +50368,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>1035</t>
@@ -49117,7 +50433,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>1035</t>
@@ -49178,7 +50498,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>1035</t>
@@ -49239,7 +50563,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>4001</t>
@@ -49300,7 +50628,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>4001</t>
@@ -49361,7 +50693,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>4001</t>
@@ -49422,7 +50758,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>4001</t>
@@ -49483,7 +50823,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>4001</t>
@@ -49544,7 +50888,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>4001</t>
@@ -49605,7 +50953,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>4001</t>
@@ -49666,7 +51018,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>4001</t>
@@ -49727,7 +51083,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>4001</t>
@@ -49788,7 +51148,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>4001</t>
@@ -49849,7 +51213,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>4001</t>
@@ -49910,7 +51278,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>4001</t>
@@ -49971,7 +51343,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>4001</t>
@@ -50032,7 +51408,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>4001</t>
@@ -50093,7 +51473,11 @@
           <t>DELTA AIR LINES</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>1035</t>
@@ -50154,7 +51538,11 @@
           <t>TRAVEL AGENCY SERVICES</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Frosch</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>1035</t>
@@ -50215,7 +51603,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>4001</t>
@@ -50276,7 +51668,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>4001</t>
@@ -50337,7 +51733,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>4001</t>
@@ -50398,7 +51798,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>4001</t>
@@ -50459,7 +51863,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>4246</t>
@@ -50520,7 +51928,11 @@
           <t>WATCHHOUSE 5TH AVE</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Watchhouse</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>4001</t>
@@ -50581,7 +51993,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>4001</t>
@@ -50642,7 +52058,11 @@
           <t>BURGERS AND BOURBON</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Burgers And Bourbon</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>1035</t>
@@ -50703,7 +52123,11 @@
           <t>BURGERS AND BOURBON</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Burgers And Bourbon</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>1035</t>
@@ -50764,7 +52188,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>1035</t>
@@ -50825,7 +52253,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>4001</t>
@@ -50886,7 +52318,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>4001</t>
@@ -50947,7 +52383,11 @@
           <t>DEVOCION - LEXINGTON NEW</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Devocion</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>4001</t>
@@ -51008,7 +52448,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>4001</t>
@@ -51069,7 +52513,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>4001</t>
@@ -51130,7 +52578,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>4001</t>
@@ -51191,7 +52643,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>4239</t>
@@ -51252,7 +52708,11 @@
           <t>GRUBHUB</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Grubhub</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>4239</t>
@@ -51313,7 +52773,11 @@
           <t>SANTA MONICA PROPER HOTEL</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Proper Hotel</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>4239</t>
@@ -51374,7 +52838,11 @@
           <t>TBIT CHAYA 003257087</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>CHAYA</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>4239</t>
@@ -51435,7 +52903,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>4239</t>
@@ -51496,7 +52968,11 @@
           <t>MSP - STONE ARCH</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Stone Arch</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>4239</t>
@@ -51557,7 +53033,11 @@
           <t>INTELSAT - DAL</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Intelsat</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>4239</t>
@@ -51618,7 +53098,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>4001</t>
@@ -51679,7 +53163,11 @@
           <t>SANTA MONICA PROPER HOTEL</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Proper Hotel</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>4239</t>
@@ -51740,7 +53228,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>4001</t>
@@ -51801,7 +53293,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>4001</t>
@@ -51862,7 +53358,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>4001</t>
@@ -51923,7 +53423,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>4001</t>
@@ -51984,7 +53488,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>1035</t>
@@ -52045,7 +53553,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>1035</t>
@@ -52106,7 +53618,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>1035</t>
@@ -52167,7 +53683,11 @@
           <t>JFK2 SHAKE SHACK B37 1051</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Shake Shack</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>4239</t>
@@ -52228,7 +53748,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>4001</t>
@@ -52289,7 +53813,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>4001</t>
@@ -52437,7 +53965,11 @@
           <t>ezCater</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Ezcater</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>3336</t>
@@ -52498,7 +54030,11 @@
           <t>ezCater</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Ezcater</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>3336</t>
@@ -52559,7 +54095,11 @@
           <t>WAL-MART SUPERCENTER 1082</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Walmart</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>3500</t>
@@ -52620,7 +54160,11 @@
           <t>AMAZON MARKEPLACE NA  PA</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>3500</t>
@@ -52681,7 +54225,11 @@
           <t>AMAZON MARKEPLACE NA  PA</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>3500</t>
@@ -52742,7 +54290,11 @@
           <t>AMAZON MARKEPLACE NA  PA</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>3500</t>
@@ -52803,7 +54355,11 @@
           <t>PUBLIX 393</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Publix</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>3500</t>
@@ -52864,7 +54420,11 @@
           <t>INSTACART</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Instacart</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>3500</t>
@@ -52925,7 +54485,11 @@
           <t>ezCater</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Ezcater</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>3369</t>
@@ -52986,7 +54550,11 @@
           <t>ezCater</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Ezcater</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>3369</t>
@@ -53047,7 +54615,11 @@
           <t>MIDTOWN TABLE</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Midtown Table</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>3500</t>
@@ -53108,7 +54680,11 @@
           <t>MIDTOWN TABLE</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Midtown Table</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>3500</t>
@@ -53169,7 +54745,11 @@
           <t>MIDTOWN TABLE</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Midtown Table</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>3500</t>
@@ -53230,7 +54810,11 @@
           <t>MIDTOWN TABLE</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Midtown Table</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>3500</t>
@@ -53291,7 +54875,11 @@
           <t>MIDTOWN TABLE</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Midtown Table</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>3500</t>
@@ -53352,7 +54940,11 @@
           <t>GRUBHUB</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Grubhub</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>3500</t>
@@ -53413,7 +55005,11 @@
           <t>GRUBHUB</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Grubhub</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>3500</t>
@@ -53478,7 +55074,11 @@
           <t>BLUE BOTTLE COFFEE</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Blue Bottle</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>3500</t>
@@ -53543,7 +55143,11 @@
           <t>UBER EATS</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Uber Eats</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>3500</t>
@@ -53608,7 +55212,11 @@
           <t>53 RESTAURANT</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>53 Restaurant</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>3500</t>
@@ -53673,7 +55281,11 @@
           <t>BLUE BOTTLE COFFEE</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Blue Bottle</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>3500</t>
@@ -53740,7 +55352,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Delta Air Lines</t>
+          <t>Delta</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -53809,7 +55421,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Delta Air Lines</t>
+          <t>Delta</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -53878,7 +55490,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Delta Air Lines</t>
+          <t>Delta</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -53947,7 +55559,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Delta Air Lines</t>
+          <t>Delta</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -54016,7 +55628,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>Frosch</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -54083,7 +55695,11 @@
           <t>UBER EATS</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Uber Eats</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>3500</t>
@@ -54148,7 +55764,11 @@
           <t>SWEETGREEN</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Sweetgreen</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>3500</t>
@@ -54213,7 +55833,11 @@
           <t>CURB-TAXI APP</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Curb</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>3500</t>
@@ -54280,7 +55904,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>United</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -54347,7 +55971,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>3285</t>
@@ -54412,7 +56040,11 @@
           <t>LONERIDER</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Lonerider</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>3285</t>
@@ -54477,7 +56109,11 @@
           <t>4254 STARBUCKS</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Starbucks</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>3285</t>
@@ -54542,7 +56178,11 @@
           <t>EWR PLAYA BOWLS #6841116</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Playa Bowls</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>3285</t>
@@ -54607,7 +56247,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>3369</t>
@@ -54672,7 +56316,11 @@
           <t>UNITED AIRLINES</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>United</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>3369</t>
@@ -54737,7 +56385,11 @@
           <t>HYATT PLACE</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Hyatt</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>3369</t>
@@ -54802,7 +56454,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>3369</t>
@@ -54867,7 +56523,11 @@
           <t>UNITED AIRLINES</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>United</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>3369</t>
@@ -54932,7 +56592,11 @@
           <t>EWR CIBO EXPRESS C90</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Cibo</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>3369</t>
@@ -54997,7 +56661,11 @@
           <t>JAX 7084 VERDI MARKET</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Verdi Market</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>3369</t>
@@ -55064,7 +56732,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Delta Air Lines</t>
+          <t>Delta</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -55133,7 +56801,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>Frosch</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -55202,7 +56870,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Delta Air Lines</t>
+          <t>Frosch</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -55271,7 +56939,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>United</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -55340,7 +57008,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>United</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -55409,7 +57077,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>United</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -55476,7 +57144,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>3353</t>
@@ -55543,7 +57215,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>United</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -55612,7 +57284,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>Frosch</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -55679,7 +57351,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>3501</t>
@@ -55744,7 +57420,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>3501</t>
@@ -55809,7 +57489,11 @@
           <t>UNITED AIRLINES</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>United</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>3285</t>
@@ -55876,7 +57560,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>Frosch</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -55945,7 +57629,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>Frosch</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -56012,7 +57696,11 @@
           <t>THE WESTIN RALEIGH-DURHAM AIRPORT</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Westin</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>3285</t>
@@ -56077,7 +57765,11 @@
           <t>THE WESTIN RALEIGH-DURHAM AIRPORT</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Westin</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>3285</t>
@@ -56142,7 +57834,11 @@
           <t>DUNKIN DONUTS 354506</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Dunkin Donuts</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>3369</t>
@@ -56207,7 +57903,11 @@
           <t>TRAVEL AGENCY SERVICES</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Frosch</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>3338</t>
@@ -56272,7 +57972,11 @@
           <t>COFFEE BEAN AND TEA LEAF SLC</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Coffee Bean &amp; Tea Leaf</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>1035</t>
@@ -56337,7 +58041,11 @@
           <t>VAA ARC</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Virgin Airways</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>3338</t>
@@ -56402,7 +58110,11 @@
           <t>DUNKIN #363849</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Dunkin</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>1035</t>
@@ -56467,7 +58179,11 @@
           <t>UNITED AIRLINES</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>United</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>1035</t>
@@ -56532,7 +58248,11 @@
           <t>DEUTSCHE LUFTHANSA BSP</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Lufthansa</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>3338</t>
@@ -56597,7 +58317,11 @@
           <t>JAMBA JUICE D61574</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Jamba Juice</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>1035</t>
@@ -56662,7 +58386,11 @@
           <t>HUDSONST1740</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Hudson News</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>1035</t>
@@ -56729,7 +58457,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>United</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -56796,7 +58524,11 @@
           <t>DUNKIN DONUTS DE6</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Dunkin Donuts</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>1035</t>
@@ -56861,7 +58593,11 @@
           <t>HUDSON ST1852</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Hudson</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>1035</t>
@@ -56926,7 +58662,11 @@
           <t>HOLIDAY INN EXPRESS PHILA</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Holiday Inn</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>1035</t>
@@ -56991,7 +58731,11 @@
           <t>TRAVEL AGENCY SERVICES</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Frosch</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>3369</t>
@@ -57056,7 +58800,11 @@
           <t>Delta</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>1035</t>
@@ -57121,7 +58869,11 @@
           <t>CMF VENDING</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>CMF Vending</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>1035</t>
@@ -57186,7 +58938,11 @@
           <t>TRAVEL AGENCY SERVICES</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Frosch</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>1035</t>
@@ -57251,7 +59007,11 @@
           <t>CMF VENDING</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>CMF Vending</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>1035</t>
@@ -57316,7 +59076,11 @@
           <t>CMF VENDING</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>CMF Vending</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>1035</t>
@@ -57383,7 +59147,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>United</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -57446,7 +59210,11 @@
           <t>United</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>United</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>3353</t>
@@ -57511,7 +59279,11 @@
           <t>United</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>United</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>3338</t>
@@ -57576,7 +59348,11 @@
           <t>United</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>United</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>1016-SBF</t>
@@ -57643,7 +59419,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>British Airways</t>
+          <t>British Air</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -57710,7 +59486,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>3369</t>
@@ -57777,7 +59557,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>British Airways</t>
+          <t>British Air</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -57846,7 +59626,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>British Airways</t>
+          <t>British Air</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -57915,7 +59695,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>British Airways</t>
+          <t>British Air</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -57984,7 +59764,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>Frosch</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -58053,7 +59833,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>Frosch</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -58122,7 +59902,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>United Airlines</t>
+          <t>Frosch</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -58189,7 +59969,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>3369</t>
@@ -58254,7 +60038,11 @@
           <t>ANGIE'S SUBS CONC. A JAX</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Angie's Subs</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>3369</t>
@@ -58319,7 +60107,11 @@
           <t>UNITED AIRLINES</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>United</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>3369</t>
@@ -58384,7 +60176,11 @@
           <t>JAX 0048 TRAVEL AT EASE</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Paradies Lagardere</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>3369</t>
@@ -58449,7 +60245,11 @@
           <t>JAX 7084 VERDI MARKET</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Verdi Market</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>3369</t>
@@ -58514,7 +60314,11 @@
           <t>EWR VANGUARD MKT</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Vanguard Market</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>3369</t>
@@ -58579,7 +60383,11 @@
           <t>AC HOTEL JACKSONVILLE ST JOHNS TOWN CENT</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>AC Hotel</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>3369</t>
@@ -58644,7 +60452,11 @@
           <t>AC HOTEL JACKSONVILLE ST JOHNS TOWN CENT</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>AC Hotel</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>3369</t>
@@ -58705,7 +60517,11 @@
           <t>SHELL OIL</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Shell Oil</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>3354</t>
@@ -58766,7 +60582,11 @@
           <t>NAPLES NATIONAL GOLF CLUB PROSHO</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Naples Golf Club</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>3354</t>
@@ -58827,7 +60647,11 @@
           <t>W HOTELS</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>W Hotels</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>3501</t>
@@ -58888,7 +60712,11 @@
           <t>GRUBHUB</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Grubhub</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>1008</t>
@@ -58949,7 +60777,11 @@
           <t>JUSTGIVING.COM PURCHASE WITH MR POINTS</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>1008</t>
@@ -59010,7 +60842,11 @@
           <t>GRUBHUB</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Grubhub</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>1008</t>
@@ -59071,7 +60907,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>3500</t>
@@ -59132,7 +60972,11 @@
           <t>JUSTGIVING.COM PURCHASE WITH MR POINTS</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>1008</t>
@@ -59193,7 +61037,11 @@
           <t>GRUBHUB</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Grubhub</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>1008</t>
@@ -59254,7 +61102,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>3431</t>
@@ -59315,7 +61167,11 @@
           <t>QDOBA 3045</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Qdoba</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>3501</t>
@@ -59376,7 +61232,11 @@
           <t>TOASTIQUE</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Toastique</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>3501</t>
@@ -59437,7 +61297,11 @@
           <t>PHL 1771 THE TODAY SHOW</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>The Today Show</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>3501</t>
@@ -59498,7 +61362,11 @@
           <t>CULINARY DROPOUT</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Culinary Dropout</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>3501</t>
@@ -59559,7 +61427,11 @@
           <t>PHL 1771 THE TODAY SHOW</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>The Today Show</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>3501</t>
@@ -59620,7 +61492,11 @@
           <t>2077 CLT TRAVEL AT EASE</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Travel At Ease</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>3501</t>
@@ -59681,7 +61557,11 @@
           <t>AMERICAN AIRLINES</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>American</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>3431</t>
@@ -59742,7 +61622,11 @@
           <t>JUSTGIVING.COM PURCHASE WITH MR POINTS</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>1008</t>
@@ -59803,7 +61687,11 @@
           <t>GRUBHUB</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Grubhub</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>1008</t>
@@ -59864,7 +61752,11 @@
           <t>W HOTELS</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>W Hotels</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>3501</t>
@@ -59925,7 +61817,11 @@
           <t>W HOTELS</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>W Hotels</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>3501</t>
@@ -59986,7 +61882,11 @@
           <t>MIDTOWN TABLE</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Midtown Table</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>3501</t>
@@ -60047,7 +61947,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>3501</t>
@@ -60108,7 +62012,11 @@
           <t>JERSEY MIKES 13231</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Jersey Mike's</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>3354</t>
@@ -60169,7 +62077,11 @@
           <t>VERSAILLES RSTR</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Versailles</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>3354</t>
@@ -60230,7 +62142,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>3501</t>
@@ -60291,7 +62207,11 @@
           <t>UBER</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Uber</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>3501</t>
@@ -60352,7 +62272,11 @@
           <t>SURFSIDE TRANSPORTATION/ BOBCAT</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Surfside</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>3431</t>
@@ -60415,7 +62339,7 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Frosch</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -60478,7 +62402,11 @@
           <t>GRUBHUB</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Grubhub</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>1008</t>
@@ -60539,7 +62467,11 @@
           <t>GRUBHUB</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Grubhub</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>1008</t>
@@ -60600,7 +62532,11 @@
           <t>SURFSIDE TRANSPORTATION/ BOBCAT</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Surfside</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>1035</t>
@@ -60661,7 +62597,11 @@
           <t>SURFSIDE TRANSPORTATION/ BOBCAT</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Surfside</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>1035</t>
@@ -60722,7 +62662,11 @@
           <t>BURGER FI JAX</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Burger Fi</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>1035</t>
@@ -60783,7 +62727,11 @@
           <t>SHELL OIL</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Shell Oil</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>3501</t>
@@ -60844,7 +62792,11 @@
           <t>JAX 0048 TRAVEL AT EASE</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Paradies Lagardere</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>1035</t>
@@ -60905,7 +62857,11 @@
           <t>HUDSON ST2165</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Hudson</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>1035</t>
@@ -60966,7 +62922,11 @@
           <t>SURFSIDE TRANSPORTATION/ BOBCAT</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Surfside</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>3501</t>
@@ -61027,7 +62987,11 @@
           <t>MARRIOTT 33737 PHIL ARPT</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Marriott</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>3431</t>
@@ -61088,7 +63052,11 @@
           <t>JUSTGIVING.COM PURCHASE WITH MR POINTS</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>1008</t>
@@ -61149,7 +63117,11 @@
           <t>JUSTGIVING.COM PURCHASE WITH MR POINTS</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>1008</t>
@@ -61210,7 +63182,11 @@
           <t>GRUBHUB</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Grubhub</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>1008</t>
@@ -61271,7 +63247,11 @@
           <t>American Express Initiated Activity</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>1008</t>
@@ -61332,7 +63312,11 @@
           <t>American Express Initiated Activity</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>1008</t>
@@ -61393,7 +63377,11 @@
           <t>GRUBHUB</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Grubhub</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>1008</t>
@@ -61454,7 +63442,11 @@
           <t>HOTEL AT AVALON</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Hotel At Avalon</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>3501</t>
@@ -61517,7 +63509,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>American</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -61582,7 +63574,7 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>Delta Air Lines</t>
+          <t>Delta</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -61647,7 +63639,7 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>Delta Air Lines</t>
+          <t>Frosch</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
@@ -61712,7 +63704,7 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>Delta Air Lines</t>
+          <t>Delta</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -61775,7 +63767,11 @@
           <t>American Express Initiated Activity</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>1008</t>
@@ -61836,7 +63832,11 @@
           <t>GRUBHUB</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Grubhub</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>1008</t>
@@ -61899,7 +63899,7 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>Delta Air Lines</t>
+          <t>Frosch</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
@@ -61964,7 +63964,7 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>Delta Air Lines</t>
+          <t>Frosch</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
@@ -62027,7 +64027,11 @@
           <t>FOUR SEASONS MIAMI EDGE R</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Four Seasons</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>3501</t>
@@ -62088,7 +64092,11 @@
           <t>TRAVEL RESERVATION USA</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Hotels.com</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>3399</t>
@@ -62149,7 +64157,11 @@
           <t>TRAVEL RESERVATION US</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Hotels.com</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>3500</t>
@@ -62305,7 +64317,11 @@
           <t>MADE MAD INC</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Made Mad</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>7500</t>
@@ -62370,7 +64386,11 @@
           <t>DELTA AIR LINES</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>1035</t>
@@ -62435,7 +64455,11 @@
           <t>ALLIANZ INSURANCE</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Allianz</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>1035</t>
@@ -62500,7 +64524,11 @@
           <t>RINALDI'S DELI</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Rinaldi's Deli</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>7500</t>
@@ -62565,7 +64593,11 @@
           <t>BERGAMO'S</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Bergamo's</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>7501</t>
@@ -62630,7 +64662,11 @@
           <t>CHICK-FIL-A # 04141</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Chick Fil A</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>7500</t>
@@ -62695,7 +64731,11 @@
           <t>Delta</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>1035</t>
@@ -62760,7 +64800,11 @@
           <t>RINALDI'S DELI</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Rinaldi's Deli</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>7500</t>
@@ -62825,7 +64869,11 @@
           <t>WWW.STAPLES.COM 472</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Staples</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>7500</t>
@@ -62890,7 +64938,11 @@
           <t>TRAVEL AGENCY SERVICES</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Frosch</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>1035</t>
